--- a/03_study_selection/final/selected_primary_studies.xlsx
+++ b/03_study_selection/final/selected_primary_studies.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="Articles" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Articles!$B$1:$U$23</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Articles!$B$1:$U$20</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="208">
   <si>
     <t>#</t>
   </si>
@@ -507,48 +507,15 @@
     <t>Cited by: 5; All Open Access; Hybrid Gold Open Access</t>
   </si>
   <si>
-    <t>Extracting the Architecture of Microservices: An Approach for Explainability and Traceability</t>
-  </si>
-  <si>
-    <t>Queval, Pierre Jean and Zdun, Uwe</t>
+    <t>Detecting and Resolving Coupling-Related Infrastructure as Code Based Architecture Smells in Microservice Deployments</t>
+  </si>
+  <si>
+    <t>IEEE International Conference on Cloud Computing, CLOUD</t>
   </si>
   <si>
     <t>2023</t>
   </si>
   <si>
-    <t>346 - 353</t>
-  </si>
-  <si>
-    <t>14212 LNCS</t>
-  </si>
-  <si>
-    <t>The polyglot nature of microservice architectures and the need for high reliability in security analyses pose unique challenges that existing approaches to automatic architecture recovery often fail to address. This article proposes an approach for extracting detailed architecture models from polyglot microservice source code focusing on explainability and traceability. The approach involves abstracting code navigation as a tree structure, using an exploratory algorithm to detect architectural aspects, and providing a set of generic detectors as input. The architecture models are automatically annotated with detailed information that makes them useful for architecture conformance checking and violation fixing. Our case studies of microservice software systems validate the usefulness of our approach, providing insights into its completeness, accuracy, and effectiveness for software architecture tasks. © 2023, The Author(s), under exclusive license to Springer Nature Switzerland AG.</t>
-  </si>
-  <si>
-    <t>10.1007/978-3-031-42592-9_24</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85172069966&amp;doi=10.1007%2F978-3-031-42592-9_24&amp;partnerID=40&amp;md5=0a4509fefe26e4240984deaa4b0a70d1</t>
-  </si>
-  <si>
-    <t>Architecture; Explainability; Microservices; Polyglot</t>
-  </si>
-  <si>
-    <t>Air navigation; Codes (symbols); Software architecture; Architecture modeling; Architecture recovery; Code navigation; Explainability; High reliability; Microservice; Polyglot; Security analysis; Source codes; Tree structures; Trees (mathematics)</t>
-  </si>
-  <si>
-    <t>Cited by: 6</t>
-  </si>
-  <si>
-    <t>Studies that propose, analyze, or evaluate methods, techniques, approaches, tools, or frameworks for ACC.</t>
-  </si>
-  <si>
-    <t>Detecting and Resolving Coupling-Related Infrastructure as Code Based Architecture Smells in Microservice Deployments</t>
-  </si>
-  <si>
-    <t>IEEE International Conference on Cloud Computing, CLOUD</t>
-  </si>
-  <si>
     <t>201 - 211</t>
   </si>
   <si>
@@ -570,48 +537,18 @@
     <t>Codes (symbols); Open source software; Architecture smell; Automatic method; Best practices; Infrastructure as code; IT infrastructures; Loose couplings; Metric; Modeling; Refactoring methods; Software resources; Odors</t>
   </si>
   <si>
-    <t>Exploring Architectural Evolution in Microservice Systems Using Repository Mining Techniques and Static Code Analysis</t>
-  </si>
-  <si>
-    <t>Genfer, Patric and Zdun, Uwe</t>
+    <t>DOMICO: Checking conformance between domain models and implementations</t>
+  </si>
+  <si>
+    <t>Zhong, Chenxing and Zhang, He and Huang, Huang and Chen, Zhikun and Li, Chao and Liu, Xiaodong and Li, Shanshan</t>
+  </si>
+  <si>
+    <t>Software - Practice and Experience</t>
   </si>
   <si>
     <t>2024</t>
   </si>
   <si>
-    <t>157 - 173</t>
-  </si>
-  <si>
-    <t>14889 LNCS</t>
-  </si>
-  <si>
-    <t>Microservices have gained popularity for isolating service functionality and mitigating issues such as architectural erosion and technical debt. However, their decentralized nature and rapid development often obscure the holistic view of the system and lead developers to lose sight of the overarching architecture. Our work addresses this challenge by proposing a novel approach to track and assess the evolution of microservice architectures through static source code analysis. We combine source code repository mining techniques with architectural reconstruction to measure various metrics throughout a system’s development history. Our approach uses a formal API-based decomposition model that can easily be adapted for different scenarios by choosing various architectural metrics. We validated our method’s scalability and robustness through a case study on an extensive open-source microservice reference system with more than 40 individual services written in different languages and more than 400 commits. Our research provides software architects with a powerful tool to identify and monitor problematic architectural trends before they become imminent threats, enabling the evolution of microservice-based systems while maintaining architectural coherence and integrity. © The Author(s), under exclusive license to Springer Nature Switzerland AG 2024.</t>
-  </si>
-  <si>
-    <t>10.1007/978-3-031-70797-1_10</t>
-  </si>
-  <si>
-    <t>https://www.scopus.com/inward/record.uri?eid=2-s2.0-85203600424&amp;doi=10.1007%2F978-3-031-70797-1_10&amp;partnerID=40&amp;md5=7a0d70dcf9868757ca1f21ec1cf1b792</t>
-  </si>
-  <si>
-    <t>evolution; metrics; Microservice API; source code detectors; source code repository mining</t>
-  </si>
-  <si>
-    <t>Problem oriented languages; Program debugging; Architectural evolution; Evolution; Metric; Microservice API; Mining techniques; Repository mining; Source code detector; Source code repositories; Source code repository mining; Source codes; Open source software</t>
-  </si>
-  <si>
-    <t>Cited by: 4</t>
-  </si>
-  <si>
-    <t>DOMICO: Checking conformance between domain models and implementations</t>
-  </si>
-  <si>
-    <t>Zhong, Chenxing and Zhang, He and Huang, Huang and Chen, Zhikun and Li, Chao and Liu, Xiaodong and Li, Shanshan</t>
-  </si>
-  <si>
-    <t>Software - Practice and Experience</t>
-  </si>
-  <si>
     <t>595 - 616</t>
   </si>
   <si>
@@ -700,30 +637,6 @@
   </si>
   <si>
     <t>Cited by: 4; All Open Access; Gold Open Access; Green Open Access</t>
-  </si>
-  <si>
-    <t>Continuous Conformance of Software Architectures</t>
-  </si>
-  <si>
-    <t>Bucaioni, Alessio and Di Salle, Amleto and Iovino, Ludovico and Mariani, Leonardo and Pelliccione, Patrizio</t>
-  </si>
-  <si>
-    <t>IEEE Digital Library</t>
-  </si>
-  <si>
-    <t>112-122</t>
-  </si>
-  <si>
-    <t>Software architectures are pivotal in the success of software-intensive systems and serve as foundational elements that significantly impact the overall software quality. Reference architectures abstract software elements, define main responsibilities and interactions within a domain, and guide the architectural design of new systems. Using reference architectures offers advantages like enhanced interoperability, cost reduction through reusability, decreased project risks, improved communication, and adherence to best practices. However, these benefits are most pronounced when software architectures align with reference architectures. Deviations from prescribed reference architectures can nullify these benefits. Uncontrolled misalignment can become prohibitively expensive, necessitating costly redevelopments, with maintenance costs reaching up to 90% of development costs. Conformance-checking processes and identifying and resolving violations in the software architecture are essential to mitigate misalignment. To address these challenges, we introduce the concept of continuous conformance that is expressed as a distance function, together with a process supporting it. Continuous conformance quantifies the degree to which a software architecture adheres to a designated reference architecture. The conformance concept enables multi-level, incremental, and non-blocking checking and restoration tasks and allows the check of partial architectures without obstructing the design process. We operationalize this process through an assistive modeling tool to architect an Internet of things-based system.</t>
-  </si>
-  <si>
-    <t>10.1109/ICSA59870.2024.00019</t>
-  </si>
-  <si>
-    <t>Costs;Software architecture;Computer architecture;Software quality;Maintenance;Internet;Task analysis;Reference architecture;conformance;modeling assistant</t>
-  </si>
-  <si>
-    <t>2835-7043</t>
   </si>
 </sst>
 </file>
@@ -1931,10 +1844,10 @@
         <v>164</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>166</v>
@@ -1971,13 +1884,13 @@
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="U17" s="3" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1">
@@ -1985,16 +1898,16 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>24</v>
@@ -2009,7 +1922,7 @@
         <v>180</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>181</v>
@@ -2028,13 +1941,13 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>33</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>34</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
@@ -2042,56 +1955,56 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>37</v>
+        <v>189</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="T19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" ht="12.75" customHeight="1">
@@ -2099,216 +2012,124 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>200</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="H20" s="4"/>
       <c r="I20" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>33</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="O21" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4"/>
-      <c r="S21" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="U21" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="J22" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="O22" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4"/>
-      <c r="S22" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="R23" s="4"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>175</v>
-      </c>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="7"/>
+      <c r="U22" s="8"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+      <c r="S23" s="5"/>
+      <c r="T23" s="7"/>
+      <c r="U23" s="8"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="5"/>
@@ -2330,13 +2151,13 @@
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
-      <c r="T24" s="5"/>
-      <c r="U24" s="5"/>
+      <c r="T24" s="7"/>
+      <c r="U24" s="8"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -2353,13 +2174,13 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="7"/>
-      <c r="U25" s="8"/>
+      <c r="T25" s="5"/>
+      <c r="U25" s="5"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2376,8 +2197,8 @@
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
-      <c r="T26" s="7"/>
-      <c r="U26" s="8"/>
+      <c r="T26" s="5"/>
+      <c r="U26" s="5"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="5"/>
@@ -2399,8 +2220,8 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="7"/>
-      <c r="U27" s="8"/>
+      <c r="T27" s="5"/>
+      <c r="U27" s="5"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="5"/>
@@ -20204,83 +20025,14 @@
       <c r="T801" s="5"/>
       <c r="U801" s="5"/>
     </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="5"/>
-      <c r="B802" s="5"/>
-      <c r="C802" s="5"/>
-      <c r="D802" s="5"/>
-      <c r="E802" s="5"/>
-      <c r="F802" s="5"/>
-      <c r="G802" s="5"/>
-      <c r="H802" s="5"/>
-      <c r="I802" s="5"/>
-      <c r="J802" s="5"/>
-      <c r="K802" s="5"/>
-      <c r="L802" s="5"/>
-      <c r="M802" s="5"/>
-      <c r="N802" s="5"/>
-      <c r="O802" s="5"/>
-      <c r="P802" s="5"/>
-      <c r="Q802" s="5"/>
-      <c r="R802" s="5"/>
-      <c r="S802" s="5"/>
-      <c r="T802" s="5"/>
-      <c r="U802" s="5"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="5"/>
-      <c r="B803" s="5"/>
-      <c r="C803" s="5"/>
-      <c r="D803" s="5"/>
-      <c r="E803" s="5"/>
-      <c r="F803" s="5"/>
-      <c r="G803" s="5"/>
-      <c r="H803" s="5"/>
-      <c r="I803" s="5"/>
-      <c r="J803" s="5"/>
-      <c r="K803" s="5"/>
-      <c r="L803" s="5"/>
-      <c r="M803" s="5"/>
-      <c r="N803" s="5"/>
-      <c r="O803" s="5"/>
-      <c r="P803" s="5"/>
-      <c r="Q803" s="5"/>
-      <c r="R803" s="5"/>
-      <c r="S803" s="5"/>
-      <c r="T803" s="5"/>
-      <c r="U803" s="5"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="5"/>
-      <c r="B804" s="5"/>
-      <c r="C804" s="5"/>
-      <c r="D804" s="5"/>
-      <c r="E804" s="5"/>
-      <c r="F804" s="5"/>
-      <c r="G804" s="5"/>
-      <c r="H804" s="5"/>
-      <c r="I804" s="5"/>
-      <c r="J804" s="5"/>
-      <c r="K804" s="5"/>
-      <c r="L804" s="5"/>
-      <c r="M804" s="5"/>
-      <c r="N804" s="5"/>
-      <c r="O804" s="5"/>
-      <c r="P804" s="5"/>
-      <c r="Q804" s="5"/>
-      <c r="R804" s="5"/>
-      <c r="S804" s="5"/>
-      <c r="T804" s="5"/>
-      <c r="U804" s="5"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$B$1:$U$23"/>
-  <conditionalFormatting sqref="T1:T804">
+  <autoFilter ref="$B$1:$U$20"/>
+  <conditionalFormatting sqref="T1:T801">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Accepted"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T1:T804">
+  <conditionalFormatting sqref="T1:T801">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Rejected"</formula>
     </cfRule>
